--- a/excels/Workshops.xlsx
+++ b/excels/Workshops.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CED TD-11\Downloads\fmain\NITW-Transportation-Division-main\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NIT\Documents\PA_Catts\Nitw_WB\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBDA5F1-26B6-4B80-A4D5-C5DD70CE1F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="12150"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TTPW" sheetId="1" r:id="rId1"/>
@@ -19,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="76">
   <si>
     <t>S.No</t>
   </si>
@@ -152,9 +156,6 @@
     <t>One Day workshop on "Need for Project Management Education in India"</t>
   </si>
   <si>
-    <t>Three Day National Transportation Young Researchers Symposium</t>
-  </si>
-  <si>
     <t>GOI</t>
   </si>
   <si>
@@ -213,12 +214,54 @@
   </si>
   <si>
     <t xml:space="preserve">DST </t>
+  </si>
+  <si>
+    <t>A One Week Workshop on “SAFE SYSTEM PERSPECTIVE ON VULNERABLE ROAD USERS IN INDIA”</t>
+  </si>
+  <si>
+    <t>A One Day Stakeholders Workshop on “Challenges Towards Zero Deaths: Adopting the Safe System in India”</t>
+  </si>
+  <si>
+    <t>Sparc , GOI</t>
+  </si>
+  <si>
+    <t>Sparc, GOI</t>
+  </si>
+  <si>
+    <t>A five-day executive development programme on Safety Evaluation of Rural Roads to Panchayat Raj and R&amp;B Engineers </t>
+  </si>
+  <si>
+    <t>Panchayat Raj</t>
+  </si>
+  <si>
+    <t>A Two Day Workshop on Sustainable Urban Transport (SUT 2013) at NIT Warangal</t>
+  </si>
+  <si>
+    <t>Ministry of Urban Development (MOUD) , GOI</t>
+  </si>
+  <si>
+    <t>One Day Workshop on “Role of Community in Construction and Maintenance of Rural Roads” to the People’s Representatives of AP</t>
+  </si>
+  <si>
+    <t>Three-day Workshop (Train the Trainer Program) on “Autodesk Software Solutions” to the Faculty of Southern India Engineering Colleges</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Autodesk India Pvt. Ltd., Bangalore.</t>
+  </si>
+  <si>
+    <t>One Day Technology Awareness Workshop on “Recent Advances in Bitumen Technology”, to the Civil Engineers of SCCL at Ramagundam</t>
+  </si>
+  <si>
+    <t>M/S Shell Bitumen</t>
+  </si>
+  <si>
+    <t>6-day workshop on “Sustainable Urban Transport: Comprehensive Transport master Plans – VISUM &amp; VISSIM (for M.Tech. TE Students)”, in association with PTV Vision, Germany</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -538,8 +581,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.28515625" customWidth="1"/>
@@ -569,7 +612,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>1969</v>
@@ -583,7 +626,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D3">
         <v>1970</v>
@@ -597,7 +640,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4">
         <v>1975</v>
@@ -611,7 +654,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5">
         <v>1975</v>
@@ -625,7 +668,7 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6">
         <v>1976</v>
@@ -639,7 +682,7 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7">
         <v>1977</v>
@@ -653,7 +696,7 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8">
         <v>1978</v>
@@ -667,7 +710,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9">
         <v>1979</v>
@@ -681,7 +724,7 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10">
         <v>1981</v>
@@ -695,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11">
         <v>1984</v>
@@ -709,7 +752,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12">
         <v>1985</v>
@@ -723,7 +766,7 @@
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13">
         <v>1985</v>
@@ -737,7 +780,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14">
         <v>1989</v>
@@ -751,7 +794,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15">
         <v>1989</v>
@@ -765,7 +808,7 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16">
         <v>1993</v>
@@ -779,7 +822,7 @@
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17">
         <v>1993</v>
@@ -793,7 +836,7 @@
         <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18">
         <v>1994</v>
@@ -807,7 +850,7 @@
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19">
         <v>1995</v>
@@ -821,7 +864,7 @@
         <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20">
         <v>1997</v>
@@ -835,7 +878,7 @@
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21">
         <v>2003</v>
@@ -849,7 +892,7 @@
         <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22">
         <v>2003</v>
@@ -863,7 +906,7 @@
         <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23">
         <v>2005</v>
@@ -874,13 +917,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
         <v>53</v>
       </c>
       <c r="D24">
-        <v>2007</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -888,13 +931,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D25">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -902,13 +945,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D26">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -916,10 +959,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27">
         <v>2008</v>
@@ -930,13 +973,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D28">
-        <v>2010</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -944,13 +987,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D29">
-        <v>2010</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -958,80 +1001,80 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D30">
-        <v>2011</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>33</v>
-      </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D31">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>33</v>
-      </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D32">
-        <v>2012</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>34</v>
-      </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D33">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D34">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D35">
         <v>2012</v>
@@ -1039,55 +1082,55 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D36">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D37">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D38">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D39">
         <v>2013</v>
@@ -1095,30 +1138,114 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D40">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" t="s">
+        <v>60</v>
+      </c>
+      <c r="D41">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" t="s">
+        <v>59</v>
+      </c>
+      <c r="D43">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>57</v>
-      </c>
-      <c r="D41">
-        <v>2014</v>
+      <c r="B44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" t="s">
+        <v>69</v>
+      </c>
+      <c r="D44">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" t="s">
+        <v>64</v>
+      </c>
+      <c r="D46">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47">
+        <v>2025</v>
       </c>
     </row>
   </sheetData>
